--- a/output/北塩原村_見込量算定のRedTeam再レビュー.xlsx
+++ b/output/北塩原村_見込量算定のRedTeam再レビュー.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>この誤りを放置すると、生活介護・就労継続支援Ｂ型について現に利用している方を見込量から除いてしまい、必要な量を過小に見込む。当方の骨子案とMECE点検では正しく定義できていたが、申し送りを書くときに短く言い換えたところで誤りが入った。照会Ｍ-23の文もあわせて直した。</t>
+          <t>この誤りを放置すると、生活介護・就労継続支援Ｂ型について現に利用している方を見込量から除いてしまい、必要な量を過小に見込む。当方の骨子案とMECE点検では正しく定義できていたが、申し送りを書くときに短く言い換えたところで誤りが入った。照会はＭ-109として分けた。</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>告示の定義は制度改正に伴う特例の対象を指す。誤った定義のままでは、生活介護・就労継続支援Ｂ型について現に利用している方を見込量から除いてしまい、必要な量を過小に見込む。照会Ｍ-23の文も、この定義に当たる方がいるかを尋ねる形に直した</t>
+          <t>告示の定義は制度改正に伴う特例の対象を指す。誤った定義のままでは、生活介護・就労継続支援Ｂ型について現に利用している方を見込量から除いてしまい、必要な量を過小に見込む。照会はＭ-23と別の事項であるためＭ-109として分けた</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2087,6 +2087,33 @@
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>令和8年10月20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Ｍ-109</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>国の基本指針は、生活介護、就労継続支援Ｂ型及び施設入所支援の必要な量の見込みについて、継続入所者の数を除いて設定するものとしています。ここでいう継続入所者とは、障害者等の地域生活を支援するための関係法律の整備に関する法律（平成22年法律第71号）による改正前の児童福祉法に規定する指定知的障害児施設等に入所していた18歳以上の方であって、同法による改正後の障害者総合支援法に基づく指定障害者支援施設等の指定を受けた当該施設に引き続き入所している方をいいます。計画期間の開始前から引き続き利用している方を広く指すものではありません。施設入所支援の利用者４人について、この定義に当たる方がいらっしゃるかをご教示ください。当たる方がいる場合は、その数を除いた量が基本指針のいう「必要な量の見込み」になります。なお、生活介護及び就労継続支援Ｂ型については、現に利用している方を見込量から除くことはしません。当初この事項はＭ-23（施設入所者４人の意向等）と同じ番号で記載していましたが、別の事項であるため番号を分けました</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>令和8年10月20日</t>
         </is>

--- a/output/北塩原村_見込量算定のRedTeam再レビュー.xlsx
+++ b/output/北塩原村_見込量算定のRedTeam再レビュー.xlsx
@@ -1662,7 +1662,7 @@
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>本村は対象となる方が少なく、一人の増減が率に大きく表れます。このため、全国の伸び率や過去の実績の延長によらず、一人ずつ積…
-［表］加減／拠り所（10行）
+［表］加減／拠り所（12行）
 そのうえで、必要な量と、実際に確保できる量とを分けて把握します。必要な量に対して、事業所の定員、空き、人材、送迎、冬季の…
 ［注記］【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の…</t>
         </is>
